--- a/downloads/loesungen/11_Projekte_3NF_Loesung.xlsx
+++ b/downloads/loesungen/11_Projekte_3NF_Loesung.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="Red25eb5a1ba94fb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="R05d0a74699fc4e0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="3" r:id="R3e1556a65dca40e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="4" r:id="R6a40614ae3b748cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="R599594a3e5764fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="R99d477dfb0814527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="3" r:id="Rb0db5f9a57cf4d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="4" r:id="R37e65dd0511848e1"/>
   </x:sheets>
 </x:workbook>
 </file>
